--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-historique-des-actes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="367">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -538,6 +538,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -727,6 +730,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -737,10 +743,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -753,6 +774,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -760,6 +790,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -767,6 +800,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1067,6 +1103,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1443,7 +1485,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -5100,7 +5142,9 @@
       <c r="K36" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L36" s="2"/>
+      <c r="L36" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5171,10 +5215,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5208,7 +5252,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>74</v>
@@ -5230,7 +5274,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5248,7 +5292,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5268,10 +5312,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5305,7 +5349,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>74</v>
@@ -5327,7 +5371,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5345,7 +5389,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5365,10 +5409,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5382,7 +5426,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5394,10 +5438,10 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5448,7 +5492,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5468,10 +5512,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5485,7 +5529,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5494,13 +5538,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5551,7 +5595,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5571,10 +5615,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5672,10 +5716,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5691,7 +5735,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5704,7 +5748,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5716,7 +5760,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5755,7 +5799,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5775,17 +5819,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>75</v>
@@ -5794,7 +5838,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5807,7 +5851,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5819,7 +5863,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5858,7 +5902,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5878,17 +5922,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5910,7 +5954,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5922,7 +5966,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5961,7 +6005,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5981,17 +6025,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6013,7 +6057,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6064,7 +6108,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6084,17 +6128,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>75</v>
@@ -6103,7 +6147,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6116,7 +6160,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6128,7 +6172,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6167,7 +6211,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6187,10 +6231,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6213,11 +6257,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6268,7 +6312,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6288,10 +6332,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6318,7 +6362,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6369,7 +6413,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6389,17 +6433,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6417,11 +6461,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6472,7 +6516,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6492,17 +6536,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6520,11 +6564,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6575,7 +6619,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6595,17 +6639,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6623,11 +6667,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6678,7 +6722,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6698,10 +6742,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6715,7 +6759,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6724,16 +6768,18 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6781,7 +6827,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6801,10 +6847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6818,7 +6864,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6827,15 +6873,17 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>74</v>
@@ -6884,7 +6932,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6904,10 +6952,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6930,12 +6978,16 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -6983,7 +7035,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7003,10 +7055,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7031,10 +7083,14 @@
       <c r="K55" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L55" s="2"/>
+      <c r="L55" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>74</v>
       </c>
@@ -7062,7 +7118,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7080,7 +7136,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7100,10 +7156,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7126,12 +7182,18 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L56" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>74</v>
       </c>
@@ -7179,7 +7241,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7199,10 +7261,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7225,12 +7287,14 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>74</v>
       </c>
@@ -7278,7 +7342,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7298,10 +7362,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7324,12 +7388,14 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>74</v>
       </c>
@@ -7377,7 +7443,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7397,10 +7463,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7414,7 +7480,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7423,7 +7489,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7464,7 +7530,7 @@
         <v>74</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -7474,7 +7540,7 @@
         <v>124</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7494,13 +7560,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>74</v>
@@ -7522,7 +7588,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7575,7 +7641,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7595,10 +7661,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7696,10 +7762,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7797,10 +7863,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7898,10 +7964,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7999,10 +8065,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8102,10 +8168,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8205,10 +8271,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8308,10 +8374,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8411,10 +8477,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8512,10 +8578,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8545,7 +8611,7 @@
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
@@ -8571,7 +8637,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8589,7 +8655,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8609,10 +8675,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8646,7 +8712,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>74</v>
@@ -8688,7 +8754,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8708,10 +8774,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8734,7 +8800,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8787,7 +8853,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8807,10 +8873,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8833,7 +8899,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8886,7 +8952,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8906,10 +8972,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8932,7 +8998,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8985,7 +9051,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9005,10 +9071,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9031,7 +9097,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9084,7 +9150,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9104,10 +9170,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9130,7 +9196,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9183,7 +9249,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9203,10 +9269,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9229,10 +9295,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9284,7 +9350,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9304,10 +9370,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9330,7 +9396,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9383,7 +9449,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9403,10 +9469,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9429,7 +9495,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9482,7 +9548,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9502,10 +9568,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9528,7 +9594,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9581,7 +9647,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9601,13 +9667,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>74</v>
@@ -9629,7 +9695,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9682,7 +9748,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9702,10 +9768,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9803,10 +9869,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9904,10 +9970,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10005,10 +10071,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10106,10 +10172,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10209,10 +10275,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10312,10 +10378,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10415,10 +10481,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10518,10 +10584,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10619,10 +10685,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10652,7 +10718,7 @@
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
@@ -10678,7 +10744,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -10696,7 +10762,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10716,10 +10782,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10753,7 +10819,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>74</v>
@@ -10795,7 +10861,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10815,10 +10881,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10841,10 +10907,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -10896,7 +10962,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10916,10 +10982,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10942,7 +11008,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10995,7 +11061,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11015,10 +11081,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11041,7 +11107,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11094,7 +11160,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11114,10 +11180,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11140,7 +11206,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11193,7 +11259,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11213,10 +11279,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11239,7 +11305,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11292,7 +11358,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11312,10 +11378,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11338,7 +11404,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11391,7 +11457,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11411,10 +11477,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11437,7 +11503,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11490,7 +11556,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11510,10 +11576,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11536,7 +11602,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11589,7 +11655,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11609,10 +11675,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11635,7 +11701,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11688,7 +11754,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11708,10 +11774,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11734,12 +11800,16 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="L102" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>74</v>
       </c>
@@ -11787,7 +11857,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11807,10 +11877,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11908,10 +11978,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12009,10 +12079,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12110,10 +12180,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12211,10 +12281,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12314,10 +12384,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12417,10 +12487,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12520,10 +12590,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12623,10 +12693,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12724,10 +12794,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12754,7 +12824,7 @@
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12763,7 +12833,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>74</v>
@@ -12805,7 +12875,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12825,10 +12895,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12862,7 +12932,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>74</v>
@@ -12904,7 +12974,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12924,10 +12994,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12950,7 +13020,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13003,7 +13073,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
